--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487780_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487780_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.4734</v>
+        <v>8.9169</v>
       </c>
       <c r="E2" t="n">
-        <v>5.5037</v>
+        <v>6.771</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9697</v>
+        <v>2.1458</v>
       </c>
       <c r="G2" t="n">
         <v>-0.5931999999999999</v>
@@ -610,13 +610,13 @@
         <v>3.1218</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5598</v>
+        <v>0.8837</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.2925</v>
+        <v>-0.0252</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7327</v>
+        <v>0.9089</v>
       </c>
       <c r="V2" t="n">
         <v>6.5452</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V. ORLOV STURMAN MAURIN</t>
+          <t>Z. WILLIAMS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.513</v>
+        <v>2.4763</v>
       </c>
       <c r="E3" t="n">
-        <v>1.1527</v>
+        <v>3.3439</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3603</v>
+        <v>-0.8675</v>
       </c>
       <c r="G3" t="n">
-        <v>1.212</v>
+        <v>-0.5901</v>
       </c>
       <c r="H3" t="n">
-        <v>2.586</v>
+        <v>-0.7999000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.374</v>
+        <v>0.2098</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5634</v>
+        <v>2.8391</v>
       </c>
       <c r="K3" t="n">
-        <v>3.4067</v>
+        <v>0.4577</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1568</v>
+        <v>2.3815</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.3515</v>
+        <v>-3.4293</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8207</v>
+        <v>-1.2576</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.5308</v>
+        <v>-2.1717</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.8325</v>
+        <v>2.7055</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.1218</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2893</v>
+        <v>2.7055</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3635</v>
+        <v>0.5909</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7111</v>
+        <v>0.0448</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6524</v>
+        <v>0.5461</v>
       </c>
       <c r="V3" t="n">
         <v>-0.23</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.4599</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.23</v>
+        <v>-0.6899</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Z. WILLIAMS</t>
+          <t>V. ORLOV STURMAN MAURIN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3315</v>
+        <v>0.8701</v>
       </c>
       <c r="E4" t="n">
-        <v>2.4633</v>
+        <v>0.5098</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.1318</v>
+        <v>0.3603</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.5901</v>
+        <v>1.212</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.7999000000000001</v>
+        <v>2.586</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2098</v>
+        <v>-1.374</v>
       </c>
       <c r="J4" t="n">
-        <v>2.8391</v>
+        <v>3.5634</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4577</v>
+        <v>3.4067</v>
       </c>
       <c r="L4" t="n">
-        <v>2.3815</v>
+        <v>0.1568</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.4293</v>
+        <v>-2.3515</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.2576</v>
+        <v>-0.8207</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.1717</v>
+        <v>-1.5308</v>
       </c>
       <c r="P4" t="n">
-        <v>2.7055</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-3.1218</v>
       </c>
       <c r="R4" t="n">
-        <v>2.7055</v>
+        <v>2.2893</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5538999999999999</v>
+        <v>0.7206</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8358</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2819</v>
+        <v>0.6524</v>
       </c>
       <c r="V4" t="n">
         <v>-0.23</v>
       </c>
       <c r="W4" t="n">
-        <v>0.4599</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.6899</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. CORREIA</t>
+          <t>A. HERRERA DOMINGUEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2891</v>
+        <v>0.5309</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4429</v>
+        <v>-0.9379</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1538</v>
+        <v>1.4688</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0968</v>
+        <v>-0.3032</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9939</v>
+        <v>0.3858</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.0907</v>
+        <v>-0.6891</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1729</v>
+        <v>-0.9441000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0554</v>
+        <v>-0.1815</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1176</v>
+        <v>-0.7625</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.2697</v>
+        <v>0.6408</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0614</v>
+        <v>0.5674</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.2083</v>
+        <v>0.0735</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.0406</v>
+        <v>0.6244</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.0406</v>
+        <v>0.6244</v>
       </c>
       <c r="S5" t="n">
-        <v>3.1342</v>
+        <v>-0.0202</v>
       </c>
       <c r="T5" t="n">
-        <v>1.8912</v>
+        <v>-0.2238</v>
       </c>
       <c r="U5" t="n">
-        <v>1.2429</v>
+        <v>0.2036</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.7076</v>
+        <v>0.23</v>
       </c>
       <c r="W5" t="n">
-        <v>0.4599</v>
+        <v>0.23</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5248</v>
+        <v>0.2817</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9197</v>
+        <v>0.794</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3949</v>
+        <v>-0.5123</v>
       </c>
       <c r="G6" t="n">
         <v>-3.9409</v>
@@ -922,13 +922,13 @@
         <v>2.7055</v>
       </c>
       <c r="S6" t="n">
-        <v>1.4033</v>
+        <v>1.1601</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7235</v>
+        <v>0.5977</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6798999999999999</v>
+        <v>0.5624</v>
       </c>
       <c r="V6" t="n">
         <v>1.3975</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. HERRERA DOMINGUEZ</t>
+          <t>S. CORREIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3218</v>
+        <v>-0.3229</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.497</v>
+        <v>0.418</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1752</v>
+        <v>-0.7409</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3032</v>
+        <v>-0.0968</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3858</v>
+        <v>0.9939</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6891</v>
+        <v>-1.0907</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.9441000000000001</v>
+        <v>1.1729</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1815</v>
+        <v>1.0554</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7625</v>
+        <v>0.1176</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6408</v>
+        <v>-1.2697</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5674</v>
+        <v>-0.0614</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0735</v>
+        <v>-1.2083</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6244</v>
+        <v>-1.0406</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6244</v>
+        <v>1.0406</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8729</v>
+        <v>1.5221</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7829</v>
+        <v>0.8663</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.09</v>
+        <v>0.6556999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>0.23</v>
+        <v>-0.7076</v>
       </c>
       <c r="W7" t="n">
-        <v>0.23</v>
+        <v>0.4599</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.2683</v>
+        <v>-3.532</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7496</v>
+        <v>-0.661</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.5187</v>
+        <v>-2.871</v>
       </c>
       <c r="G8" t="n">
         <v>-1.3159</v>
@@ -1078,13 +1078,13 @@
         <v>2.2893</v>
       </c>
       <c r="S8" t="n">
-        <v>1.5482</v>
+        <v>1.2844</v>
       </c>
       <c r="T8" t="n">
-        <v>0.332</v>
+        <v>0.4206</v>
       </c>
       <c r="U8" t="n">
-        <v>1.2162</v>
+        <v>0.8639</v>
       </c>
       <c r="V8" t="n">
         <v>-1.6275</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.3836</v>
+        <v>-4.0541</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.2457</v>
+        <v>-3.1805</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1378</v>
+        <v>-0.8736</v>
       </c>
       <c r="G9" t="n">
         <v>-3.7331</v>
@@ -1156,13 +1156,13 @@
         <v>1.0406</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1905</v>
+        <v>0.139</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2643</v>
+        <v>-0.199</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0737</v>
+        <v>0.338</v>
       </c>
       <c r="V9" t="n">
         <v>-0.4599</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.5131</v>
+        <v>-4.2168</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4932</v>
+        <v>-2.2556</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.0199</v>
+        <v>-1.9612</v>
       </c>
       <c r="G10" t="n">
         <v>-3.7418</v>
@@ -1234,13 +1234,13 @@
         <v>1.8731</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2094</v>
+        <v>0.08690000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3295</v>
+        <v>-0.0919</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1201</v>
+        <v>0.1788</v>
       </c>
       <c r="V10" t="n">
         <v>-0.3538</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.3550000000000004</v>
+        <v>0.9500999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>3.4968</v>
+        <v>4.8017</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.851699999999999</v>
+        <v>-3.851599999999999</v>
       </c>
       <c r="G11" t="n">
         <v>-13.103</v>
@@ -1288,7 +1288,7 @@
         <v>6.9621</v>
       </c>
       <c r="K11" t="n">
-        <v>3.962199999999999</v>
+        <v>3.9622</v>
       </c>
       <c r="L11" t="n">
         <v>3.0004</v>
@@ -1312,10 +1312,10 @@
         <v>17.6901</v>
       </c>
       <c r="S11" t="n">
-        <v>5.0627</v>
+        <v>6.3675</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1528000000000001</v>
+        <v>1.4576</v>
       </c>
       <c r="U11" t="n">
         <v>4.9098</v>
@@ -1327,13 +1327,13 @@
         <v>10.9499</v>
       </c>
       <c r="X11" t="n">
-        <v>-6.385999999999999</v>
+        <v>-6.386</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>I. ORDOÑEZ OCHOA</t>
+          <t>J. GARCIA-ABRIL GUERRERO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.7066</v>
+        <v>2.8794</v>
       </c>
       <c r="E12" t="n">
-        <v>2.5852</v>
+        <v>0.6359</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1214</v>
+        <v>2.2435</v>
       </c>
       <c r="G12" t="n">
-        <v>2.8641</v>
+        <v>0.7714</v>
       </c>
       <c r="H12" t="n">
-        <v>2.5694</v>
+        <v>0.5803</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2947</v>
+        <v>0.191</v>
       </c>
       <c r="J12" t="n">
-        <v>4.722</v>
+        <v>0.2327</v>
       </c>
       <c r="K12" t="n">
-        <v>3.7904</v>
+        <v>0.1151</v>
       </c>
       <c r="L12" t="n">
-        <v>0.9315</v>
+        <v>0.1176</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.8578</v>
+        <v>0.5387</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.221</v>
+        <v>0.4652</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.6368</v>
+        <v>0.0735</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.2487</v>
+        <v>1.4568</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.1218</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.8731</v>
+        <v>1.4568</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1259</v>
+        <v>-0.5164</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3948</v>
+        <v>-0.7643</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2689</v>
+        <v>0.248</v>
       </c>
       <c r="V12" t="n">
-        <v>1.217</v>
+        <v>1.1675</v>
       </c>
       <c r="W12" t="n">
-        <v>1.3798</v>
+        <v>1.1675</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.1627</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. GARCIA-ABRIL GUERRERO</t>
+          <t>I. ORDOÑEZ OCHOA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.3754</v>
+        <v>2.39</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4216</v>
+        <v>2.4781</v>
       </c>
       <c r="F13" t="n">
-        <v>1.9538</v>
+        <v>-0.0881</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7714</v>
+        <v>2.8641</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5803</v>
+        <v>2.5694</v>
       </c>
       <c r="I13" t="n">
-        <v>0.191</v>
+        <v>0.2947</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2327</v>
+        <v>4.722</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1151</v>
+        <v>3.7904</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1176</v>
+        <v>0.9315</v>
       </c>
       <c r="M13" t="n">
-        <v>0.5387</v>
+        <v>-1.8578</v>
       </c>
       <c r="N13" t="n">
-        <v>0.4652</v>
+        <v>-1.221</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0735</v>
+        <v>-0.6368</v>
       </c>
       <c r="P13" t="n">
-        <v>1.4568</v>
+        <v>-1.2487</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-3.1218</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4568</v>
+        <v>1.8731</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0204</v>
+        <v>-0.4425</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9786</v>
+        <v>-0.5019</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0417</v>
+        <v>0.0595</v>
       </c>
       <c r="V13" t="n">
-        <v>1.1675</v>
+        <v>1.217</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1675</v>
+        <v>1.3798</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.1627</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. ISERN MAZA</t>
+          <t>P. MARIN FONTAN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.7905</v>
+        <v>1.7229</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9997</v>
+        <v>3.2446</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2092</v>
+        <v>-1.5216</v>
       </c>
       <c r="G14" t="n">
-        <v>4.5369</v>
+        <v>5.4096</v>
       </c>
       <c r="H14" t="n">
-        <v>1.7399</v>
+        <v>-0.1641</v>
       </c>
       <c r="I14" t="n">
-        <v>2.797</v>
+        <v>5.5737</v>
       </c>
       <c r="J14" t="n">
-        <v>5.3209</v>
+        <v>6.5325</v>
       </c>
       <c r="K14" t="n">
-        <v>1.5646</v>
+        <v>0.4281</v>
       </c>
       <c r="L14" t="n">
-        <v>3.7563</v>
+        <v>6.1044</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.784</v>
+        <v>-1.1229</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1753</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.9593</v>
+        <v>-0.5306999999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>-3.3299</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q14" t="n">
-        <v>-5.2029</v>
+        <v>-2.0812</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8731</v>
+        <v>1.6649</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2975</v>
+        <v>-0.7726</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3295</v>
+        <v>-0.8529</v>
       </c>
       <c r="U14" t="n">
-        <v>0.032</v>
+        <v>0.0803</v>
       </c>
       <c r="V14" t="n">
-        <v>0.8809</v>
+        <v>-2.4978</v>
       </c>
       <c r="W14" t="n">
-        <v>2.2112</v>
+        <v>-0.3538</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.3303</v>
+        <v>-2.144</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. MARIN FONTAN</t>
+          <t>P. ISERN MAZA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3721</v>
+        <v>1.5429</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9231</v>
+        <v>1.7854</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.551</v>
+        <v>-0.2424</v>
       </c>
       <c r="G15" t="n">
-        <v>5.4096</v>
+        <v>4.5369</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1641</v>
+        <v>1.7399</v>
       </c>
       <c r="I15" t="n">
-        <v>5.5737</v>
+        <v>2.797</v>
       </c>
       <c r="J15" t="n">
-        <v>6.5325</v>
+        <v>5.3209</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4281</v>
+        <v>1.5646</v>
       </c>
       <c r="L15" t="n">
-        <v>6.1044</v>
+        <v>3.7563</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.1229</v>
+        <v>-0.784</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5921999999999999</v>
+        <v>0.1753</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5306999999999999</v>
+        <v>-0.9593</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.4162</v>
+        <v>-3.3299</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.0812</v>
+        <v>-5.2029</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6649</v>
+        <v>1.8731</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1234</v>
+        <v>-0.5451</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.1744</v>
+        <v>-0.5438</v>
       </c>
       <c r="U15" t="n">
-        <v>0.051</v>
+        <v>-0.0012</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.4978</v>
+        <v>0.8809</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.3538</v>
+        <v>2.2112</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.144</v>
+        <v>-1.3303</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. TAIWO</t>
+          <t>I. HANEY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2216</v>
+        <v>-0.5625</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.32</v>
+        <v>0.2333</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5416</v>
+        <v>-0.7957</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.5429</v>
+        <v>2.9494</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.8466</v>
+        <v>-0.4004</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3037</v>
+        <v>3.3498</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9229000000000001</v>
+        <v>4.6031</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.0176</v>
+        <v>1.1513</v>
       </c>
       <c r="L16" t="n">
-        <v>0.9405</v>
+        <v>3.4518</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.4658</v>
+        <v>-1.6537</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.829</v>
+        <v>-1.5516</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6368</v>
+        <v>-0.102</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4162</v>
+        <v>-2.9137</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.0812</v>
+        <v>-5.2029</v>
       </c>
       <c r="R16" t="n">
-        <v>2.4974</v>
+        <v>2.2893</v>
       </c>
       <c r="S16" t="n">
-        <v>1.5547</v>
+        <v>-0.952</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8383</v>
+        <v>-0.9182</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7164</v>
+        <v>-0.0339</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.2064</v>
+        <v>0.3538</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.7513</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2064</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. HANEY</t>
+          <t>S. TAIWO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.3791</v>
+        <v>-1.3975</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0882</v>
+        <v>-1.4988</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2909</v>
+        <v>0.1013</v>
       </c>
       <c r="G17" t="n">
-        <v>2.9494</v>
+        <v>-0.5429</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.4004</v>
+        <v>-0.8466</v>
       </c>
       <c r="I17" t="n">
-        <v>3.3498</v>
+        <v>0.3037</v>
       </c>
       <c r="J17" t="n">
-        <v>4.6031</v>
+        <v>0.9229000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>1.1513</v>
+        <v>-0.0176</v>
       </c>
       <c r="L17" t="n">
-        <v>3.4518</v>
+        <v>0.9405</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.6537</v>
+        <v>-1.4658</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.5516</v>
+        <v>-0.829</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.102</v>
+        <v>-0.6368</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.9137</v>
+        <v>0.4162</v>
       </c>
       <c r="Q17" t="n">
-        <v>-5.2029</v>
+        <v>-2.0812</v>
       </c>
       <c r="R17" t="n">
-        <v>2.2893</v>
+        <v>2.4974</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.7687</v>
+        <v>-0.0644</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.2396</v>
+        <v>-0.3405</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5291</v>
+        <v>0.276</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3538</v>
+        <v>-1.2064</v>
       </c>
       <c r="W17" t="n">
-        <v>1.7513</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.3975</v>
+        <v>-1.2064</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.2354</v>
+        <v>-2.1942</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.9271</v>
+        <v>-1.4984</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.3084</v>
+        <v>-0.6957</v>
       </c>
       <c r="G18" t="n">
         <v>-1.8117</v>
@@ -1858,13 +1858,13 @@
         <v>2.4974</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.2371</v>
+        <v>-1.1959</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.2396</v>
+        <v>-0.8110000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.9975000000000001</v>
+        <v>-0.3849</v>
       </c>
       <c r="V18" t="n">
         <v>-1.6841</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.4968</v>
+        <v>-3.3119</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.7426</v>
+        <v>-1.5283</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.7542</v>
+        <v>-1.7835</v>
       </c>
       <c r="G19" t="n">
         <v>-1.0737</v>
@@ -1936,13 +1936,13 @@
         <v>0.4162</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0443</v>
+        <v>0.1406</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3915</v>
+        <v>-0.1771</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3471</v>
+        <v>0.3178</v>
       </c>
       <c r="V19" t="n">
         <v>-2.795</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3549000000000007</v>
+        <v>1.0691</v>
       </c>
       <c r="E20" t="n">
-        <v>3.8517</v>
+        <v>3.851800000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.496899999999999</v>
+        <v>-2.7822</v>
       </c>
       <c r="G20" t="n">
         <v>13.1031</v>
@@ -2014,13 +2014,13 @@
         <v>14.5682</v>
       </c>
       <c r="S20" t="n">
-        <v>-5.0626</v>
+        <v>-4.3483</v>
       </c>
       <c r="T20" t="n">
-        <v>-4.9097</v>
+        <v>-4.909700000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1529000000000001</v>
+        <v>0.5616000000000001</v>
       </c>
       <c r="V20" t="n">
         <v>-4.5641</v>
